--- a/artfynd/A 47230-2024 artfynd.xlsx
+++ b/artfynd/A 47230-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121152590</v>
+        <v>121152589</v>
       </c>
       <c r="B2" t="n">
-        <v>79679</v>
+        <v>92004</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1968</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476416</v>
+        <v>476314</v>
       </c>
       <c r="R2" t="n">
-        <v>6845970</v>
+        <v>6845800</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152589</v>
+        <v>121152590</v>
       </c>
       <c r="B3" t="n">
-        <v>91994</v>
+        <v>79682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1968</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476314</v>
+        <v>476416</v>
       </c>
       <c r="R3" t="n">
-        <v>6845800</v>
+        <v>6845970</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 47230-2024 artfynd.xlsx
+++ b/artfynd/A 47230-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121152589</v>
+        <v>121152590</v>
       </c>
       <c r="B2" t="n">
-        <v>92004</v>
+        <v>79682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1968</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476314</v>
+        <v>476416</v>
       </c>
       <c r="R2" t="n">
-        <v>6845800</v>
+        <v>6845970</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152590</v>
+        <v>121152589</v>
       </c>
       <c r="B3" t="n">
-        <v>79682</v>
+        <v>92004</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1968</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476416</v>
+        <v>476314</v>
       </c>
       <c r="R3" t="n">
-        <v>6845970</v>
+        <v>6845800</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 47230-2024 artfynd.xlsx
+++ b/artfynd/A 47230-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121152590</v>
       </c>
       <c r="B2" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121152589</v>
       </c>
       <c r="B3" t="n">
-        <v>92004</v>
+        <v>92016</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 47230-2024 artfynd.xlsx
+++ b/artfynd/A 47230-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121152590</v>
+        <v>121152589</v>
       </c>
       <c r="B2" t="n">
-        <v>79685</v>
+        <v>92017</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1968</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476416</v>
+        <v>476314</v>
       </c>
       <c r="R2" t="n">
-        <v>6845970</v>
+        <v>6845800</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152589</v>
+        <v>121152590</v>
       </c>
       <c r="B3" t="n">
-        <v>92016</v>
+        <v>79685</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1968</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476314</v>
+        <v>476416</v>
       </c>
       <c r="R3" t="n">
-        <v>6845800</v>
+        <v>6845970</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 47230-2024 artfynd.xlsx
+++ b/artfynd/A 47230-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121152589</v>
       </c>
       <c r="B2" t="n">
-        <v>92017</v>
+        <v>92020</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121152590</v>
       </c>
       <c r="B3" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 47230-2024 artfynd.xlsx
+++ b/artfynd/A 47230-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121152589</v>
+        <v>121152590</v>
       </c>
       <c r="B2" t="n">
-        <v>92020</v>
+        <v>79688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1968</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476314</v>
+        <v>476416</v>
       </c>
       <c r="R2" t="n">
-        <v>6845800</v>
+        <v>6845970</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152590</v>
+        <v>121152589</v>
       </c>
       <c r="B3" t="n">
-        <v>79688</v>
+        <v>92020</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1968</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476416</v>
+        <v>476314</v>
       </c>
       <c r="R3" t="n">
-        <v>6845970</v>
+        <v>6845800</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 47230-2024 artfynd.xlsx
+++ b/artfynd/A 47230-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121152590</v>
+        <v>121152589</v>
       </c>
       <c r="B2" t="n">
-        <v>79688</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1968</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476416</v>
+        <v>476314</v>
       </c>
       <c r="R2" t="n">
-        <v>6845970</v>
+        <v>6845800</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152589</v>
+        <v>121152590</v>
       </c>
       <c r="B3" t="n">
-        <v>92020</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1968</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476314</v>
+        <v>476416</v>
       </c>
       <c r="R3" t="n">
-        <v>6845800</v>
+        <v>6845970</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
